--- a/output/2026-10-03_11_Malesia_Perlis_Cleaning.xlsx
+++ b/output/2026-10-03_11_Malesia_Perlis_Cleaning.xlsx
@@ -489,11 +489,9 @@
           <t>Cleaning</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Importatore/distributore di attrezzature professionali per pulizia pavimenti, heavy-duty, chemicals, igiene. Distributore ufficiale dichiarato di Nilfisk, RCM SPA, FASA, 3M, REN. Sede Subang Jaya, Selangor (non in Perlis, copertura non confermata).</t>
+          <t>Importatore/distributore di attrezzature professionali per pulizia pavimenti, heavy-duty, chemicals, igiene. Distributore ufficiale dichiarato di Nilfisk, RCM SPA, FASA, 3M, REN. Sede Subang Jaya, Selangor (non in Perlis, copertura non confermata). [DUPLICATO — vedi anche: 2026-10-02_17_Malesia_Pahang_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -523,11 +521,9 @@
           <t>Cleaning</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Distributore di macchine/utensili/chimici per pulizia industriale, istituzionale e municipale, attivo dal 1971 nel Sud-Est asiatico. Sede Malaysia: Bukit Naga Industrial Park, Shah Alam, Selangor. Telefono/email Malaysia non reperiti.</t>
+          <t>Distributore di macchine/utensili/chimici per pulizia industriale, istituzionale e municipale, attivo dal 1971 nel Sud-Est asiatico. Sede Malaysia: Bukit Naga Industrial Park, Shah Alam, Selangor. Telefono/email Malaysia non reperiti. [DUPLICATO — vedi anche: 2026-10-02_17_Malesia_Pahang_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -562,10 +558,9 @@
           <t>+60 3 8070 2826</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Distributore di spazzatrici industriali/stradali/aeroportuali. Fondata 1996, membro Malaysian-German Chamber of Commerce. Rappresenta Bucher Municipal, Beam A/S, Hako-Werke, PowerBoss Minuteman. Sede Puchong, Selangor (non in Perlis).</t>
+          <t>Distributore di spazzatrici industriali/stradali/aeroportuali. Fondata 1996, membro Malaysian-German Chamber of Commerce. Rappresenta Bucher Municipal, Beam A/S, Hako-Werke, PowerBoss Minuteman. Sede Puchong, Selangor (non in Perlis). [DUPLICATO — vedi anche: 2026-10-02_17_Malesia_Pahang_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -595,11 +590,9 @@
           <t>Cleaning</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Distributore ufficiale Tennant (sweepers/scrubbers) oltre a material handling/automazione. Copertura nazionale dichiarata ma nessuna filiale a Perlis confermata. Telefono corporate non specifico alla divisione cleaning, lasciato vuoto.</t>
+          <t>Distributore ufficiale Tennant (sweepers/scrubbers) oltre a material handling/automazione. Copertura nazionale dichiarata ma nessuna filiale a Perlis confermata. Telefono corporate non specifico alla divisione cleaning, lasciato vuoto. [DUPLICATO — vedi anche: 2026-10-02_17_Malesia_Pahang_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -646,7 +639,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -671,8 +664,6 @@
           <t>Cleaning</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Rivenditore e-commerce (sede Ampang, Selangor, fondato 2007) con categoria 'Cleaning &amp; Vacuum Tools' tra i prodotti (incl. Karcher). Attivita principale hardware/tools generico; copertura e-commerce nazionale non specifica a Perlis.</t>
@@ -680,7 +671,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>

--- a/output/2026-10-03_11_Malesia_Perlis_Cleaning.xlsx
+++ b/output/2026-10-03_11_Malesia_Perlis_Cleaning.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Produttore/distributore diretto. Sede Shah Alam, Selangor; centri anche a Penang e Johor Bahru. Nessuna filiale a Perlis confermata.</t>
+          <t>Produttore/distributore diretto. Sede Shah Alam, Selangor; centri anche a Penang e Johor Bahru. Nessuna filiale a Perlis confermata. [DUPLICATO — vedi anche: 2026-10-02_17_Malesia_Pahang_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
